--- a/data/macro/China/Taiwan Export.xlsx
+++ b/data/macro/China/Taiwan Export.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\China\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\China\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{238E1545-23B8-4774-B983-24B7C27ED0D5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C83D9D4F-C47B-46EF-A000-2D70990AAB6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13980" windowHeight="7365" xr2:uid="{696C4E50-B2D2-406E-8FD7-1C3C49A10F1B}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{696C4E50-B2D2-406E-8FD7-1C3C49A10F1B}"/>
   </bookViews>
   <sheets>
     <sheet name="Taiwan Export" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="12">
   <si>
     <t>Release Date</t>
   </si>
@@ -76,8 +76,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="180" formatCode="0.0%"/>
+    <numFmt numFmtId="177" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="178" formatCode="0.0%"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -172,16 +172,16 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -499,20 +499,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03C4376D-A458-42DB-8BE7-3CEB15B1B3CC}">
-  <dimension ref="A1:G531"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G532"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="12.6" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.44140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14" style="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.85546875" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.28515625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.88671875" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" style="11" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11" style="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="4"/>
+    <col min="8" max="16384" width="9.109375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>7</v>
       </c>
@@ -535,7 +535,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="5">
         <v>29952</v>
       </c>
@@ -552,7 +552,7 @@
         <v>4.0899999999999999E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="5">
         <v>29983</v>
       </c>
@@ -572,7 +572,7 @@
         <v>4.0899999999999999E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="5">
         <v>30011</v>
       </c>
@@ -592,7 +592,7 @@
         <v>9.3600000000000003E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="5">
         <v>30042</v>
       </c>
@@ -612,7 +612,7 @@
         <v>2.46E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="5">
         <v>30072</v>
       </c>
@@ -632,7 +632,7 @@
         <v>-1.0200000000000001E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="5">
         <v>30103</v>
       </c>
@@ -652,7 +652,7 @@
         <v>-4.2599999999999999E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="5">
         <v>30133</v>
       </c>
@@ -672,7 +672,7 @@
         <v>-4.5600000000000002E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="5">
         <v>30164</v>
       </c>
@@ -692,7 +692,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="5">
         <v>30195</v>
       </c>
@@ -712,7 +712,7 @@
         <v>-0.13289999999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="5">
         <v>30225</v>
       </c>
@@ -732,7 +732,7 @@
         <v>-1.5E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="5">
         <v>30256</v>
       </c>
@@ -752,7 +752,7 @@
         <v>-0.1075</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="5">
         <v>30286</v>
       </c>
@@ -772,7 +772,7 @@
         <v>-2.8299999999999999E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="5">
         <v>30317</v>
       </c>
@@ -792,7 +792,7 @@
         <v>6.93E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="5">
         <v>30348</v>
       </c>
@@ -812,7 +812,7 @@
         <v>-3.6900000000000002E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="5">
         <v>30376</v>
       </c>
@@ -832,7 +832,7 @@
         <v>2.3400000000000001E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="5">
         <v>30407</v>
       </c>
@@ -852,7 +852,7 @@
         <v>-3.9E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="5">
         <v>30437</v>
       </c>
@@ -872,7 +872,7 @@
         <v>0.10630000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="5">
         <v>30468</v>
       </c>
@@ -892,7 +892,7 @@
         <v>8.3599999999999994E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="5">
         <v>30498</v>
       </c>
@@ -912,7 +912,7 @@
         <v>0.18179999999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="5">
         <v>30529</v>
       </c>
@@ -932,7 +932,7 @@
         <v>0.1542</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="5">
         <v>30560</v>
       </c>
@@ -952,7 +952,7 @@
         <v>0.2049</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="5">
         <v>30590</v>
       </c>
@@ -972,7 +972,7 @@
         <v>0.1895</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="5">
         <v>30621</v>
       </c>
@@ -992,7 +992,7 @@
         <v>0.22869999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="5">
         <v>30651</v>
       </c>
@@ -1012,7 +1012,7 @@
         <v>0.32350000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="5">
         <v>30682</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>0.12790000000000001</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="5">
         <v>30713</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>0.41339999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="5">
         <v>30742</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>0.2112</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="5">
         <v>30773</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>0.38219999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="5">
         <v>30803</v>
       </c>
@@ -1112,7 +1112,7 @@
         <v>0.24460000000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="5">
         <v>30834</v>
       </c>
@@ -1132,7 +1132,7 @@
         <v>0.34050000000000002</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="5">
         <v>30864</v>
       </c>
@@ -1152,7 +1152,7 @@
         <v>0.2198</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="5">
         <v>30895</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>0.25979999999999998</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="5">
         <v>30926</v>
       </c>
@@ -1192,7 +1192,7 @@
         <v>0.15440000000000001</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="5">
         <v>30956</v>
       </c>
@@ -1212,7 +1212,7 @@
         <v>0.12039999999999999</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="5">
         <v>30987</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>0.24229999999999999</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="5">
         <v>31017</v>
       </c>
@@ -1252,7 +1252,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="5">
         <v>31048</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>2.5899999999999999E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="5">
         <v>31079</v>
       </c>
@@ -1292,7 +1292,7 @@
         <v>0.1623</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="5">
         <v>31107</v>
       </c>
@@ -1312,7 +1312,7 @@
         <v>0.1095</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="5">
         <v>31138</v>
       </c>
@@ -1332,7 +1332,7 @@
         <v>-9.2700000000000005E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="5">
         <v>31168</v>
       </c>
@@ -1352,7 +1352,7 @@
         <v>3.5400000000000001E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="5">
         <v>31199</v>
       </c>
@@ -1372,7 +1372,7 @@
         <v>-8.4000000000000005E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="5">
         <v>31229</v>
       </c>
@@ -1392,7 +1392,7 @@
         <v>-1.8800000000000001E-2</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="5">
         <v>31260</v>
       </c>
@@ -1412,7 +1412,7 @@
         <v>-5.1900000000000002E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="5">
         <v>31291</v>
       </c>
@@ -1432,7 +1432,7 @@
         <v>-0.10199999999999999</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="5">
         <v>31321</v>
       </c>
@@ -1452,7 +1452,7 @@
         <v>5.5500000000000001E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="5">
         <v>31352</v>
       </c>
@@ -1472,7 +1472,7 @@
         <v>-1.8499999999999999E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" s="5">
         <v>31382</v>
       </c>
@@ -1492,7 +1492,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" s="5">
         <v>31413</v>
       </c>
@@ -1512,7 +1512,7 @@
         <v>0.1018</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" s="5">
         <v>31444</v>
       </c>
@@ -1532,7 +1532,7 @@
         <v>0.13159999999999999</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" s="5">
         <v>31472</v>
       </c>
@@ -1552,7 +1552,7 @@
         <v>8.5500000000000007E-2</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" s="5">
         <v>31503</v>
       </c>
@@ -1572,7 +1572,7 @@
         <v>0.33289999999999997</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" s="5">
         <v>31533</v>
       </c>
@@ -1592,7 +1592,7 @@
         <v>0.17080000000000001</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" s="5">
         <v>31564</v>
       </c>
@@ -1612,7 +1612,7 @@
         <v>0.1875</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" s="5">
         <v>31594</v>
       </c>
@@ -1632,7 +1632,7 @@
         <v>0.26200000000000001</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" s="5">
         <v>31625</v>
       </c>
@@ -1652,7 +1652,7 @@
         <v>0.2959</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" s="5">
         <v>31656</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>0.45729999999999998</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" s="5">
         <v>31686</v>
       </c>
@@ -1692,7 +1692,7 @@
         <v>0.2576</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" s="5">
         <v>31717</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>0.4824</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" s="5">
         <v>31747</v>
       </c>
@@ -1732,7 +1732,7 @@
         <v>0.44569999999999999</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" s="5">
         <v>31778</v>
       </c>
@@ -1752,7 +1752,7 @@
         <v>0.4219</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" s="5">
         <v>31809</v>
       </c>
@@ -1772,7 +1772,7 @@
         <v>7.8399999999999997E-2</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" s="5">
         <v>31837</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>0.68369999999999997</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" s="5">
         <v>31868</v>
       </c>
@@ -1812,7 +1812,7 @@
         <v>0.36730000000000002</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" s="5">
         <v>31898</v>
       </c>
@@ -1832,7 +1832,7 @@
         <v>0.39810000000000001</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" s="5">
         <v>31929</v>
       </c>
@@ -1852,7 +1852,7 @@
         <v>0.40060000000000001</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" s="5">
         <v>31959</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>0.48110000000000003</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" s="5">
         <v>31990</v>
       </c>
@@ -1892,7 +1892,7 @@
         <v>0.2437</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" s="5">
         <v>32021</v>
       </c>
@@ -1912,7 +1912,7 @@
         <v>0.36499999999999999</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A71" s="5">
         <v>32051</v>
       </c>
@@ -1932,7 +1932,7 @@
         <v>0.59589999999999999</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A72" s="5">
         <v>32082</v>
       </c>
@@ -1952,7 +1952,7 @@
         <v>0.10580000000000001</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A73" s="5">
         <v>32112</v>
       </c>
@@ -1972,7 +1972,7 @@
         <v>0.34739999999999999</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A74" s="5">
         <v>32143</v>
       </c>
@@ -1992,7 +1992,7 @@
         <v>0.24590000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="5">
         <v>32174</v>
       </c>
@@ -2012,7 +2012,7 @@
         <v>0.46750000000000003</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A76" s="5">
         <v>32203</v>
       </c>
@@ -2032,7 +2032,7 @@
         <v>0.1143</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A77" s="5">
         <v>32234</v>
       </c>
@@ -2052,7 +2052,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A78" s="5">
         <v>32264</v>
       </c>
@@ -2072,7 +2072,7 @@
         <v>9.5299999999999996E-2</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A79" s="5">
         <v>32295</v>
       </c>
@@ -2092,7 +2092,7 @@
         <v>0.2296</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A80" s="5">
         <v>32325</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>6.7400000000000002E-2</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="5">
         <v>32356</v>
       </c>
@@ -2132,7 +2132,7 @@
         <v>0.17150000000000001</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="5">
         <v>32387</v>
       </c>
@@ -2152,7 +2152,7 @@
         <v>0.15359999999999999</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A83" s="5">
         <v>32417</v>
       </c>
@@ -2172,7 +2172,7 @@
         <v>-0.1241</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A84" s="5">
         <v>32448</v>
       </c>
@@ -2192,7 +2192,7 @@
         <v>0.26750000000000002</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="5">
         <v>32478</v>
       </c>
@@ -2212,7 +2212,7 @@
         <v>5.3999999999999999E-2</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A86" s="5">
         <v>32509</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>0.1061</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A87" s="5">
         <v>32540</v>
       </c>
@@ -2252,7 +2252,7 @@
         <v>9.01E-2</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A88" s="5">
         <v>32568</v>
       </c>
@@ -2272,7 +2272,7 @@
         <v>-4.5100000000000001E-2</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="5">
         <v>32599</v>
       </c>
@@ -2292,7 +2292,7 @@
         <v>0.21340000000000001</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="5">
         <v>32629</v>
       </c>
@@ -2312,7 +2312,7 @@
         <v>0.1681</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A91" s="5">
         <v>32660</v>
       </c>
@@ -2332,7 +2332,7 @@
         <v>0.1638</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A92" s="5">
         <v>32690</v>
       </c>
@@ -2352,7 +2352,7 @@
         <v>-6.1999999999999998E-3</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="5">
         <v>32721</v>
       </c>
@@ -2372,7 +2372,7 @@
         <v>0.22359999999999999</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="5">
         <v>32752</v>
       </c>
@@ -2392,7 +2392,7 @@
         <v>4.1099999999999998E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A95" s="5">
         <v>32782</v>
       </c>
@@ -2412,7 +2412,7 @@
         <v>0.1686</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A96" s="5">
         <v>32813</v>
       </c>
@@ -2432,7 +2432,7 @@
         <v>5.5500000000000001E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="5">
         <v>32843</v>
       </c>
@@ -2452,7 +2452,7 @@
         <v>1.1299999999999999E-2</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A98" s="5">
         <v>32874</v>
       </c>
@@ -2472,7 +2472,7 @@
         <v>4.6800000000000001E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A99" s="5">
         <v>32905</v>
       </c>
@@ -2492,7 +2492,7 @@
         <v>-7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="5">
         <v>32933</v>
       </c>
@@ -2512,7 +2512,7 @@
         <v>0.22900000000000001</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A101" s="5">
         <v>32964</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>-4.2200000000000001E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A102" s="5">
         <v>32994</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>1.41E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A103" s="5">
         <v>33025</v>
       </c>
@@ -2572,7 +2572,7 @@
         <v>-0.1014</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="5">
         <v>33055</v>
       </c>
@@ -2592,7 +2592,7 @@
         <v>1.1000000000000001E-3</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A105" s="5">
         <v>33086</v>
       </c>
@@ -2612,7 +2612,7 @@
         <v>-2.3300000000000001E-2</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A106" s="5">
         <v>33117</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>-2.93E-2</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A107" s="5">
         <v>33147</v>
       </c>
@@ -2652,7 +2652,7 @@
         <v>6.6500000000000004E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="5">
         <v>33178</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>8.5599999999999996E-2</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A109" s="5">
         <v>33208</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>0.1027</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A110" s="5">
         <v>33239</v>
       </c>
@@ -2712,7 +2712,7 @@
         <v>2.63E-2</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A111" s="5">
         <v>33270</v>
       </c>
@@ -2732,7 +2732,7 @@
         <v>0.25659999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A112" s="5">
         <v>33298</v>
       </c>
@@ -2752,7 +2752,7 @@
         <v>-2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A113" s="5">
         <v>33329</v>
       </c>
@@ -2772,7 +2772,7 @@
         <v>8.4099999999999994E-2</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A114" s="5">
         <v>33359</v>
       </c>
@@ -2792,7 +2792,7 @@
         <v>-1.17E-2</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="5">
         <v>33390</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>0.2054</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A116" s="5">
         <v>33420</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>0.30959999999999999</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A117" s="5">
         <v>33451</v>
       </c>
@@ -2852,7 +2852,7 @@
         <v>0.14050000000000001</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="5">
         <v>33482</v>
       </c>
@@ -2872,7 +2872,7 @@
         <v>7.1300000000000002E-2</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="5">
         <v>33512</v>
       </c>
@@ -2892,7 +2892,7 @@
         <v>0.2472</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A120" s="5">
         <v>33543</v>
       </c>
@@ -2912,7 +2912,7 @@
         <v>7.2599999999999998E-2</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="5">
         <v>33573</v>
       </c>
@@ -2932,7 +2932,7 @@
         <v>0.15640000000000001</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A122" s="5">
         <v>33604</v>
       </c>
@@ -2952,7 +2952,7 @@
         <v>0.1343</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A123" s="5">
         <v>33635</v>
       </c>
@@ -2972,7 +2972,7 @@
         <v>0.1173</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A124" s="5">
         <v>33664</v>
       </c>
@@ -2992,7 +2992,7 @@
         <v>6.6199999999999995E-2</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A125" s="5">
         <v>33695</v>
       </c>
@@ -3012,7 +3012,7 @@
         <v>0.21879999999999999</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A126" s="5">
         <v>33725</v>
       </c>
@@ -3032,7 +3032,7 @@
         <v>0.24379999999999999</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A127" s="5">
         <v>33756</v>
       </c>
@@ -3052,7 +3052,7 @@
         <v>3.15E-2</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A128" s="5">
         <v>33786</v>
       </c>
@@ -3072,7 +3072,7 @@
         <v>-1.5E-3</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="5">
         <v>33817</v>
       </c>
@@ -3092,7 +3092,7 @@
         <v>-2.63E-2</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A130" s="5">
         <v>33848</v>
       </c>
@@ -3112,7 +3112,7 @@
         <v>0.18579999999999999</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A131" s="5">
         <v>33878</v>
       </c>
@@ -3132,7 +3132,7 @@
         <v>-6.4399999999999999E-2</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A132" s="5">
         <v>33909</v>
       </c>
@@ -3152,7 +3152,7 @@
         <v>6.4399999999999999E-2</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A133" s="5">
         <v>33939</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>7.1800000000000003E-2</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="5">
         <v>33970</v>
       </c>
@@ -3192,7 +3192,7 @@
         <v>3.4700000000000002E-2</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A135" s="5">
         <v>34001</v>
       </c>
@@ -3212,7 +3212,7 @@
         <v>-8.4400000000000003E-2</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A136" s="5">
         <v>34029</v>
       </c>
@@ -3232,7 +3232,7 @@
         <v>0.21540000000000001</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A137" s="5">
         <v>34060</v>
       </c>
@@ -3252,7 +3252,7 @@
         <v>7.0300000000000001E-2</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A138" s="5">
         <v>34090</v>
       </c>
@@ -3272,7 +3272,7 @@
         <v>-9.1999999999999998E-3</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A139" s="5">
         <v>34121</v>
       </c>
@@ -3292,7 +3292,7 @@
         <v>0.1489</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A140" s="5">
         <v>34151</v>
       </c>
@@ -3312,7 +3312,7 @@
         <v>2.5499999999999998E-2</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A141" s="5">
         <v>34182</v>
       </c>
@@ -3332,7 +3332,7 @@
         <v>4.9500000000000002E-2</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A142" s="5">
         <v>34213</v>
       </c>
@@ -3352,7 +3352,7 @@
         <v>4.8500000000000001E-2</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A143" s="5">
         <v>34243</v>
       </c>
@@ -3372,7 +3372,7 @@
         <v>-6.8999999999999999E-3</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A144" s="5">
         <v>34274</v>
       </c>
@@ -3392,7 +3392,7 @@
         <v>6.0699999999999997E-2</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A145" s="5">
         <v>34304</v>
       </c>
@@ -3412,7 +3412,7 @@
         <v>3.8E-3</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="5">
         <v>34335</v>
       </c>
@@ -3432,7 +3432,7 @@
         <v>8.2100000000000006E-2</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A147" s="5">
         <v>34366</v>
       </c>
@@ -3452,7 +3452,7 @@
         <v>0.16700000000000001</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A148" s="5">
         <v>34394</v>
       </c>
@@ -3472,7 +3472,7 @@
         <v>-8.8300000000000003E-2</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A149" s="5">
         <v>34425</v>
       </c>
@@ -3492,7 +3492,7 @@
         <v>-2.7300000000000001E-2</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A150" s="5">
         <v>34455</v>
       </c>
@@ -3512,7 +3512,7 @@
         <v>9.69E-2</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A151" s="5">
         <v>34486</v>
       </c>
@@ -3532,7 +3532,7 @@
         <v>6.3399999999999998E-2</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A152" s="5">
         <v>34516</v>
       </c>
@@ -3552,7 +3552,7 @@
         <v>2.8799999999999999E-2</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A153" s="5">
         <v>34547</v>
       </c>
@@ -3572,7 +3572,7 @@
         <v>8.6699999999999999E-2</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A154" s="5">
         <v>34578</v>
       </c>
@@ -3592,7 +3592,7 @@
         <v>4.9000000000000002E-2</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A155" s="5">
         <v>34608</v>
       </c>
@@ -3612,7 +3612,7 @@
         <v>0.1822</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A156" s="5">
         <v>34639</v>
       </c>
@@ -3632,7 +3632,7 @@
         <v>0.18129999999999999</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A157" s="5">
         <v>34669</v>
       </c>
@@ -3652,7 +3652,7 @@
         <v>0.2591</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A158" s="5">
         <v>34700</v>
       </c>
@@ -3672,7 +3672,7 @@
         <v>0.1618</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A159" s="5">
         <v>34731</v>
       </c>
@@ -3692,7 +3692,7 @@
         <v>4.1000000000000003E-3</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A160" s="5">
         <v>34759</v>
       </c>
@@ -3712,7 +3712,7 @@
         <v>0.48060000000000003</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A161" s="5">
         <v>34790</v>
       </c>
@@ -3732,7 +3732,7 @@
         <v>0.25950000000000001</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A162" s="5">
         <v>34820</v>
       </c>
@@ -3752,7 +3752,7 @@
         <v>0.26719999999999999</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A163" s="5">
         <v>34851</v>
       </c>
@@ -3772,7 +3772,7 @@
         <v>0.18340000000000001</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A164" s="5">
         <v>34881</v>
       </c>
@@ -3792,7 +3792,7 @@
         <v>0.19939999999999999</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="5">
         <v>34912</v>
       </c>
@@ -3812,7 +3812,7 @@
         <v>0.30690000000000001</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A166" s="5">
         <v>34943</v>
       </c>
@@ -3832,7 +3832,7 @@
         <v>0.24399999999999999</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A167" s="5">
         <v>34973</v>
       </c>
@@ -3852,7 +3852,7 @@
         <v>0.1507</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A168" s="5">
         <v>35004</v>
       </c>
@@ -3872,7 +3872,7 @@
         <v>0.2029</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A169" s="5">
         <v>35034</v>
       </c>
@@ -3892,7 +3892,7 @@
         <v>5.9700000000000003E-2</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A170" s="5">
         <v>35065</v>
       </c>
@@ -3912,7 +3912,7 @@
         <v>0.16300000000000001</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A171" s="5">
         <v>35096</v>
       </c>
@@ -3932,7 +3932,7 @@
         <v>0.4501</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A172" s="5">
         <v>35125</v>
       </c>
@@ -3952,7 +3952,7 @@
         <v>-0.1115</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="5">
         <v>35156</v>
       </c>
@@ -3972,7 +3972,7 @@
         <v>-1.6000000000000001E-3</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A174" s="5">
         <v>35186</v>
       </c>
@@ -3992,7 +3992,7 @@
         <v>5.4800000000000001E-2</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A175" s="5">
         <v>35217</v>
       </c>
@@ -4012,7 +4012,7 @@
         <v>-4.7899999999999998E-2</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A176" s="5">
         <v>35247</v>
       </c>
@@ -4032,7 +4032,7 @@
         <v>0.1246</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A177" s="5">
         <v>35278</v>
       </c>
@@ -4052,7 +4052,7 @@
         <v>-7.3099999999999998E-2</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A178" s="5">
         <v>35309</v>
       </c>
@@ -4072,7 +4072,7 @@
         <v>-2.06E-2</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A179" s="5">
         <v>35339</v>
       </c>
@@ -4092,7 +4092,7 @@
         <v>0.12559999999999999</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A180" s="5">
         <v>35370</v>
       </c>
@@ -4112,7 +4112,7 @@
         <v>-6.8400000000000002E-2</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A181" s="5">
         <v>35400</v>
       </c>
@@ -4132,7 +4132,7 @@
         <v>2.9499999999999998E-2</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A182" s="5">
         <v>35431</v>
       </c>
@@ -4152,7 +4152,7 @@
         <v>0.1062</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A183" s="5">
         <v>35462</v>
       </c>
@@ -4172,7 +4172,7 @@
         <v>-3.27E-2</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A184" s="5">
         <v>35490</v>
       </c>
@@ -4192,7 +4192,7 @@
         <v>2.5600000000000001E-2</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A185" s="5">
         <v>35521</v>
       </c>
@@ -4212,7 +4212,7 @@
         <v>0.1867</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A186" s="5">
         <v>35551</v>
       </c>
@@ -4232,7 +4232,7 @@
         <v>-2.29E-2</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A187" s="5">
         <v>35582</v>
       </c>
@@ -4252,7 +4252,7 @@
         <v>6.7900000000000002E-2</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A188" s="5">
         <v>35612</v>
       </c>
@@ -4272,7 +4272,7 @@
         <v>3.3300000000000003E-2</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A189" s="5">
         <v>35643</v>
       </c>
@@ -4292,7 +4292,7 @@
         <v>0.13089999999999999</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="5">
         <v>35674</v>
       </c>
@@ -4312,7 +4312,7 @@
         <v>-1.7500000000000002E-2</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A191" s="5">
         <v>35704</v>
       </c>
@@ -4332,7 +4332,7 @@
         <v>0.10639999999999999</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A192" s="5">
         <v>35735</v>
       </c>
@@ -4352,7 +4352,7 @@
         <v>6.54E-2</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A193" s="5">
         <v>35765</v>
       </c>
@@ -4372,7 +4372,7 @@
         <v>0.1157</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="5">
         <v>35796</v>
       </c>
@@ -4392,7 +4392,7 @@
         <v>2.7799999999999998E-2</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A195" s="5">
         <v>35827</v>
       </c>
@@ -4412,7 +4412,7 @@
         <v>-0.26269999999999999</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="5">
         <v>35855</v>
       </c>
@@ -4432,7 +4432,7 @@
         <v>0.12509999999999999</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A197" s="5">
         <v>35886</v>
       </c>
@@ -4452,7 +4452,7 @@
         <v>-8.0999999999999996E-3</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A198" s="5">
         <v>35916</v>
       </c>
@@ -4472,7 +4472,7 @@
         <v>-7.5300000000000006E-2</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A199" s="5">
         <v>35947</v>
       </c>
@@ -4492,7 +4492,7 @@
         <v>-7.9399999999999998E-2</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A200" s="5">
         <v>35977</v>
       </c>
@@ -4512,7 +4512,7 @@
         <v>-8.6199999999999999E-2</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A201" s="5">
         <v>36008</v>
       </c>
@@ -4532,7 +4532,7 @@
         <v>-0.16259999999999999</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A202" s="5">
         <v>36039</v>
       </c>
@@ -4552,7 +4552,7 @@
         <v>1.34E-2</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A203" s="5">
         <v>36069</v>
       </c>
@@ -4572,7 +4572,7 @@
         <v>-0.1226</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A204" s="5">
         <v>36100</v>
       </c>
@@ -4592,7 +4592,7 @@
         <v>-0.17119999999999999</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="5">
         <v>36130</v>
       </c>
@@ -4612,7 +4612,7 @@
         <v>-8.9300000000000004E-2</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A206" s="5">
         <v>36161</v>
       </c>
@@ -4632,7 +4632,7 @@
         <v>-0.13270000000000001</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A207" s="5">
         <v>36192</v>
       </c>
@@ -4652,7 +4652,7 @@
         <v>0.28860000000000002</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A208" s="5">
         <v>36220</v>
       </c>
@@ -4672,7 +4672,7 @@
         <v>-0.1283</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A209" s="5">
         <v>36251</v>
       </c>
@@ -4692,7 +4692,7 @@
         <v>-1.84E-2</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A210" s="5">
         <v>36281</v>
       </c>
@@ -4712,7 +4712,7 @@
         <v>4.4999999999999997E-3</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A211" s="5">
         <v>36312</v>
       </c>
@@ -4732,7 +4732,7 @@
         <v>0.1343</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A212" s="5">
         <v>36342</v>
       </c>
@@ -4752,7 +4752,7 @@
         <v>7.9899999999999999E-2</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A213" s="5">
         <v>36373</v>
       </c>
@@ -4772,7 +4772,7 @@
         <v>0.11409999999999999</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A214" s="5">
         <v>36404</v>
       </c>
@@ -4792,7 +4792,7 @@
         <v>0.1106</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A215" s="5">
         <v>36434</v>
       </c>
@@ -4812,7 +4812,7 @@
         <v>7.9000000000000008E-3</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A216" s="5">
         <v>36465</v>
       </c>
@@ -4832,7 +4832,7 @@
         <v>0.32619999999999999</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A217" s="5">
         <v>36495</v>
       </c>
@@ -4852,7 +4852,7 @@
         <v>0.1099</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A218" s="5">
         <v>36526</v>
       </c>
@@ -4872,7 +4872,7 @@
         <v>0.20899999999999999</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A219" s="5">
         <v>36557</v>
       </c>
@@ -4892,7 +4892,7 @@
         <v>0.22339999999999999</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A220" s="5">
         <v>36586</v>
       </c>
@@ -4912,7 +4912,7 @@
         <v>0.19500000000000001</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A221" s="5">
         <v>36617</v>
       </c>
@@ -4932,7 +4932,7 @@
         <v>0.1583</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A222" s="5">
         <v>36647</v>
       </c>
@@ -4952,7 +4952,7 @@
         <v>0.35360000000000003</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" s="5">
         <v>36678</v>
       </c>
@@ -4972,7 +4972,7 @@
         <v>0.24579999999999999</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" s="5">
         <v>36708</v>
       </c>
@@ -4992,7 +4992,7 @@
         <v>0.26860000000000001</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A225" s="5">
         <v>36739</v>
       </c>
@@ -5012,7 +5012,7 @@
         <v>0.374</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A226" s="5">
         <v>36770</v>
       </c>
@@ -5032,7 +5032,7 @@
         <v>0.1986</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A227" s="5">
         <v>36800</v>
       </c>
@@ -5052,7 +5052,7 @@
         <v>0.36499999999999999</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" s="5">
         <v>36831</v>
       </c>
@@ -5072,7 +5072,7 @@
         <v>0.1963</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A229" s="5">
         <v>36861</v>
       </c>
@@ -5092,7 +5092,7 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" s="5">
         <v>36892</v>
       </c>
@@ -5112,7 +5112,7 @@
         <v>0.10349999999999999</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A231" s="5">
         <v>36923</v>
       </c>
@@ -5132,7 +5132,7 @@
         <v>-0.1762</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A232" s="5">
         <v>36951</v>
       </c>
@@ -5152,7 +5152,7 @@
         <v>0.12859999999999999</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A233" s="5">
         <v>36982</v>
       </c>
@@ -5172,7 +5172,7 @@
         <v>-0.02</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A234" s="5">
         <v>37012</v>
       </c>
@@ -5192,7 +5192,7 @@
         <v>-0.1147</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A235" s="5">
         <v>37043</v>
       </c>
@@ -5212,7 +5212,7 @@
         <v>-0.2273</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A236" s="5">
         <v>37073</v>
       </c>
@@ -5232,7 +5232,7 @@
         <v>-0.16750000000000001</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A237" s="5">
         <v>37104</v>
       </c>
@@ -5252,7 +5252,7 @@
         <v>-0.28179999999999999</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A238" s="5">
         <v>37135</v>
       </c>
@@ -5272,7 +5272,7 @@
         <v>-0.25280000000000002</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A239" s="5">
         <v>37165</v>
       </c>
@@ -5292,7 +5292,7 @@
         <v>-0.3145</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A240" s="5">
         <v>37196</v>
       </c>
@@ -5312,7 +5312,7 @@
         <v>-0.15190000000000001</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A241" s="5">
         <v>37226</v>
       </c>
@@ -5332,7 +5332,7 @@
         <v>-0.19270000000000001</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A242" s="5">
         <v>37257</v>
       </c>
@@ -5352,7 +5352,7 @@
         <v>-0.14299999999999999</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A243" s="5">
         <v>37288</v>
       </c>
@@ -5372,7 +5372,7 @@
         <v>-2.0999999999999999E-3</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A244" s="5">
         <v>37316</v>
       </c>
@@ -5392,7 +5392,7 @@
         <v>-0.2019</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A245" s="5">
         <v>37347</v>
       </c>
@@ -5412,7 +5412,7 @@
         <v>-7.7000000000000002E-3</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A246" s="5">
         <v>37377</v>
       </c>
@@ -5432,7 +5432,7 @@
         <v>1.1299999999999999E-2</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A247" s="5">
         <v>37408</v>
       </c>
@@ -5452,7 +5452,7 @@
         <v>9.69E-2</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A248" s="5">
         <v>37438</v>
       </c>
@@ -5472,7 +5472,7 @@
         <v>9.6600000000000005E-2</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A249" s="5">
         <v>37469</v>
       </c>
@@ -5492,7 +5492,7 @@
         <v>0.15440000000000001</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A250" s="5">
         <v>37500</v>
       </c>
@@ -5512,7 +5512,7 @@
         <v>0.156</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A251" s="5">
         <v>37530</v>
       </c>
@@ -5532,7 +5532,7 @@
         <v>0.28610000000000002</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A252" s="5">
         <v>37561</v>
       </c>
@@ -5552,7 +5552,7 @@
         <v>3.8E-3</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A253" s="5">
         <v>37591</v>
       </c>
@@ -5572,7 +5572,7 @@
         <v>0.17430000000000001</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A254" s="5">
         <v>37622</v>
       </c>
@@ -5592,7 +5592,7 @@
         <v>0.1424</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A255" s="5">
         <v>37653</v>
       </c>
@@ -5612,7 +5612,7 @@
         <v>4.41E-2</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A256" s="5">
         <v>37681</v>
       </c>
@@ -5632,7 +5632,7 @@
         <v>0.22839999999999999</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A257" s="5">
         <v>37712</v>
       </c>
@@ -5652,7 +5652,7 @@
         <v>0.1084</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A258" s="5">
         <v>37742</v>
       </c>
@@ -5672,7 +5672,7 @@
         <v>6.88E-2</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A259" s="5">
         <v>37773</v>
       </c>
@@ -5692,7 +5692,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A260" s="5">
         <v>37803</v>
       </c>
@@ -5712,7 +5712,7 @@
         <v>4.1200000000000001E-2</v>
       </c>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A261" s="5">
         <v>37834</v>
       </c>
@@ -5732,7 +5732,7 @@
         <v>5.3400000000000003E-2</v>
       </c>
     </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A262" s="5">
         <v>37865</v>
       </c>
@@ -5752,7 +5752,7 @@
         <v>0.1454</v>
       </c>
     </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A263" s="5">
         <v>37895</v>
       </c>
@@ -5772,7 +5772,7 @@
         <v>0.1239</v>
       </c>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A264" s="5">
         <v>37926</v>
       </c>
@@ -5792,7 +5792,7 @@
         <v>0.14899999999999999</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A265" s="5">
         <v>37956</v>
       </c>
@@ -5812,7 +5812,7 @@
         <v>0.17269999999999999</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A266" s="5">
         <v>37987</v>
       </c>
@@ -5832,7 +5832,7 @@
         <v>0.20660000000000001</v>
       </c>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A267" s="5">
         <v>38018</v>
       </c>
@@ -5852,7 +5852,7 @@
         <v>0.18060000000000001</v>
       </c>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A268" s="5">
         <v>38047</v>
       </c>
@@ -5872,7 +5872,7 @@
         <v>0.35930000000000001</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A269" s="5">
         <v>38078</v>
       </c>
@@ -5892,7 +5892,7 @@
         <v>0.1701</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A270" s="5">
         <v>38108</v>
       </c>
@@ -5912,7 +5912,7 @@
         <v>0.22320000000000001</v>
       </c>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A271" s="5">
         <v>38139</v>
       </c>
@@ -5932,7 +5932,7 @@
         <v>0.4052</v>
       </c>
     </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A272" s="5">
         <v>38169</v>
       </c>
@@ -5952,7 +5952,7 @@
         <v>0.25659999999999999</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A273" s="5">
         <v>38200</v>
       </c>
@@ -5972,7 +5972,7 @@
         <v>0.2626</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A274" s="5">
         <v>38231</v>
       </c>
@@ -5992,7 +5992,7 @@
         <v>0.1971</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A275" s="5">
         <v>38261</v>
       </c>
@@ -6012,7 +6012,7 @@
         <v>0.18779999999999999</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A276" s="5">
         <v>38292</v>
       </c>
@@ -6032,7 +6032,7 @@
         <v>0.18140000000000001</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A277" s="5">
         <v>38322</v>
       </c>
@@ -6052,7 +6052,7 @@
         <v>0.12820000000000001</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A278" s="5">
         <v>38353</v>
       </c>
@@ -6072,7 +6072,7 @@
         <v>6.2899999999999998E-2</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A279" s="5">
         <v>38384</v>
       </c>
@@ -6092,7 +6092,7 @@
         <v>0.30349999999999999</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A280" s="5">
         <v>38412</v>
       </c>
@@ -6112,7 +6112,7 @@
         <v>-0.1154</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A281" s="5">
         <v>38443</v>
       </c>
@@ -6132,7 +6132,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A282" s="5">
         <v>38473</v>
       </c>
@@ -6152,7 +6152,7 @@
         <v>0.1119</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A283" s="5">
         <v>38504</v>
       </c>
@@ -6172,7 +6172,7 @@
         <v>4.3099999999999999E-2</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A284" s="5">
         <v>38534</v>
       </c>
@@ -6192,7 +6192,7 @@
         <v>2.3099999999999999E-2</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A285" s="5">
         <v>38565</v>
       </c>
@@ -6212,7 +6212,7 @@
         <v>5.2699999999999997E-2</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A286" s="5">
         <v>38596</v>
       </c>
@@ -6232,7 +6232,7 @@
         <v>7.4200000000000002E-2</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A287" s="5">
         <v>38626</v>
       </c>
@@ -6252,7 +6252,7 @@
         <v>8.6900000000000005E-2</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A288" s="5">
         <v>38657</v>
       </c>
@@ -6272,7 +6272,7 @@
         <v>0.16520000000000001</v>
       </c>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A289" s="5">
         <v>38687</v>
       </c>
@@ -6292,7 +6292,7 @@
         <v>0.108</v>
       </c>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A290" s="5">
         <v>38718</v>
       </c>
@@ -6312,7 +6312,7 @@
         <v>0.153</v>
       </c>
     </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A291" s="5">
         <v>38749</v>
       </c>
@@ -6332,7 +6332,7 @@
         <v>4.4900000000000002E-2</v>
       </c>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A292" s="5">
         <v>38777</v>
       </c>
@@ -6352,7 +6352,7 @@
         <v>0.26329999999999998</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A293" s="5">
         <v>38808</v>
       </c>
@@ -6372,7 +6372,7 @@
         <v>8.4400000000000003E-2</v>
       </c>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A294" s="5">
         <v>38838</v>
       </c>
@@ -6392,7 +6392,7 @@
         <v>0.14979999999999999</v>
       </c>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A295" s="5">
         <v>38869</v>
       </c>
@@ -6412,7 +6412,7 @@
         <v>0.10440000000000001</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A296" s="5">
         <v>38899</v>
       </c>
@@ -6432,7 +6432,7 @@
         <v>0.1651</v>
       </c>
     </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A297" s="5">
         <v>38930</v>
       </c>
@@ -6452,7 +6452,7 @@
         <v>0.2112</v>
       </c>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A298" s="5">
         <v>38961</v>
       </c>
@@ -6472,7 +6472,7 @@
         <v>0.16619999999999999</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A299" s="5">
         <v>38991</v>
       </c>
@@ -6492,7 +6492,7 @@
         <v>0.1812</v>
       </c>
     </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A300" s="5">
         <v>39022</v>
       </c>
@@ -6512,7 +6512,7 @@
         <v>5.5800000000000002E-2</v>
       </c>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A301" s="5">
         <v>39052</v>
       </c>
@@ -6532,7 +6532,7 @@
         <v>8.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A302" s="5">
         <v>39083</v>
       </c>
@@ -6552,7 +6552,7 @@
         <v>9.2499999999999999E-2</v>
       </c>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A303" s="5">
         <v>39114</v>
       </c>
@@ -6572,7 +6572,7 @@
         <v>0.17549999999999999</v>
       </c>
     </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A304" s="5">
         <v>39142</v>
       </c>
@@ -6592,7 +6592,7 @@
         <v>-3.6499999999999998E-2</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A305" s="5">
         <v>39173</v>
       </c>
@@ -6612,7 +6612,7 @@
         <v>0.1042</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A306" s="5">
         <v>39203</v>
       </c>
@@ -6632,7 +6632,7 @@
         <v>5.4699999999999999E-2</v>
       </c>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A307" s="5">
         <v>39234</v>
       </c>
@@ -6652,7 +6652,7 @@
         <v>3.4799999999999998E-2</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A308" s="5">
         <v>39264</v>
       </c>
@@ -6672,7 +6672,7 @@
         <v>0.1096</v>
       </c>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A309" s="5">
         <v>39295</v>
       </c>
@@ -6692,7 +6692,7 @@
         <v>8.2100000000000006E-2</v>
       </c>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A310" s="5">
         <v>39326</v>
       </c>
@@ -6712,7 +6712,7 @@
         <v>0.10059999999999999</v>
       </c>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A311" s="5">
         <v>39356</v>
       </c>
@@ -6732,7 +6732,7 @@
         <v>0.106</v>
       </c>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A312" s="5">
         <v>39387</v>
       </c>
@@ -6752,7 +6752,7 @@
         <v>0.14349999999999999</v>
       </c>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A313" s="5">
         <v>39417</v>
       </c>
@@ -6772,7 +6772,7 @@
         <v>0.1193</v>
       </c>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A314" s="5">
         <v>39448</v>
       </c>
@@ -6792,7 +6792,7 @@
         <v>0.19739999999999999</v>
       </c>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A315" s="5">
         <v>39479</v>
       </c>
@@ -6812,7 +6812,7 @@
         <v>0.11849999999999999</v>
       </c>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A316" s="5">
         <v>39508</v>
       </c>
@@ -6832,7 +6832,7 @@
         <v>0.18290000000000001</v>
       </c>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A317" s="5">
         <v>39539</v>
       </c>
@@ -6852,7 +6852,7 @@
         <v>0.22689999999999999</v>
       </c>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A318" s="5">
         <v>39569</v>
       </c>
@@ -6872,7 +6872,7 @@
         <v>0.13930000000000001</v>
       </c>
     </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A319" s="5">
         <v>39600</v>
       </c>
@@ -6892,7 +6892,7 @@
         <v>0.20480000000000001</v>
       </c>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A320" s="5">
         <v>39630</v>
       </c>
@@ -6912,7 +6912,7 @@
         <v>0.2122</v>
       </c>
     </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A321" s="5">
         <v>39661</v>
       </c>
@@ -6932,7 +6932,7 @@
         <v>7.9100000000000004E-2</v>
       </c>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A322" s="5">
         <v>39692</v>
       </c>
@@ -6952,7 +6952,7 @@
         <v>0.18229999999999999</v>
       </c>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A323" s="5">
         <v>39722</v>
       </c>
@@ -6972,7 +6972,7 @@
         <v>-1.6400000000000001E-2</v>
       </c>
     </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A324" s="5">
         <v>39753</v>
       </c>
@@ -6992,7 +6992,7 @@
         <v>-8.3199999999999996E-2</v>
       </c>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A325" s="5">
         <v>39783</v>
       </c>
@@ -7012,7 +7012,7 @@
         <v>-0.23319999999999999</v>
       </c>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A326" s="5">
         <v>39814</v>
       </c>
@@ -7032,7 +7032,7 @@
         <v>-0.41930000000000001</v>
       </c>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A327" s="5">
         <v>39845</v>
       </c>
@@ -7052,7 +7052,7 @@
         <v>-0.44119999999999998</v>
       </c>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A328" s="5">
         <v>39873</v>
       </c>
@@ -7072,7 +7072,7 @@
         <v>-0.2858</v>
       </c>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A329" s="5">
         <v>39904</v>
       </c>
@@ -7092,7 +7092,7 @@
         <v>-0.3579</v>
       </c>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A330" s="5">
         <v>39934</v>
       </c>
@@ -7112,7 +7112,7 @@
         <v>-0.34279999999999999</v>
       </c>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A331" s="5">
         <v>39965</v>
       </c>
@@ -7132,7 +7132,7 @@
         <v>-0.3145</v>
       </c>
     </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A332" s="5">
         <v>39995</v>
       </c>
@@ -7152,7 +7152,7 @@
         <v>-0.30380000000000001</v>
       </c>
     </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A333" s="5">
         <v>40026</v>
       </c>
@@ -7172,7 +7172,7 @@
         <v>-0.24490000000000001</v>
       </c>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A334" s="5">
         <v>40057</v>
       </c>
@@ -7192,7 +7192,7 @@
         <v>-0.2465</v>
       </c>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A335" s="5">
         <v>40087</v>
       </c>
@@ -7212,7 +7212,7 @@
         <v>-0.12720000000000001</v>
       </c>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A336" s="5">
         <v>40118</v>
       </c>
@@ -7232,7 +7232,7 @@
         <v>-4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A337" s="5">
         <v>40148</v>
       </c>
@@ -7252,7 +7252,7 @@
         <v>0.1933</v>
       </c>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A338" s="5">
         <v>40179</v>
       </c>
@@ -7272,7 +7272,7 @@
         <v>0.46829999999999999</v>
       </c>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A339" s="5">
         <v>40210</v>
       </c>
@@ -7292,7 +7292,7 @@
         <v>0.75749999999999995</v>
       </c>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A340" s="5">
         <v>40238</v>
       </c>
@@ -7312,7 +7312,7 @@
         <v>0.32600000000000001</v>
       </c>
     </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A341" s="5">
         <v>40269</v>
       </c>
@@ -7332,7 +7332,7 @@
         <v>0.50070000000000003</v>
       </c>
     </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A342" s="5">
         <v>40299</v>
       </c>
@@ -7352,7 +7352,7 @@
         <v>0.47689999999999999</v>
       </c>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A343" s="5">
         <v>40330</v>
       </c>
@@ -7372,7 +7372,7 @@
         <v>0.5746</v>
       </c>
     </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A344" s="5">
         <v>40360</v>
       </c>
@@ -7392,7 +7392,7 @@
         <v>0.34060000000000001</v>
       </c>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A345" s="5">
         <v>40391</v>
       </c>
@@ -7412,7 +7412,7 @@
         <v>0.3846</v>
       </c>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A346" s="5">
         <v>40422</v>
       </c>
@@ -7432,7 +7432,7 @@
         <v>0.26590000000000003</v>
       </c>
     </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A347" s="5">
         <v>40452</v>
       </c>
@@ -7452,7 +7452,7 @@
         <v>0.17460000000000001</v>
       </c>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A348" s="5">
         <v>40483</v>
       </c>
@@ -7472,7 +7472,7 @@
         <v>0.21909999999999999</v>
       </c>
     </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A349" s="5">
         <v>40513</v>
       </c>
@@ -7492,7 +7492,7 @@
         <v>0.21779999999999999</v>
       </c>
     </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A350" s="5">
         <v>40544</v>
       </c>
@@ -7512,7 +7512,7 @@
         <v>0.18959999999999999</v>
       </c>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A351" s="5">
         <v>40575</v>
       </c>
@@ -7532,7 +7532,7 @@
         <v>0.16550000000000001</v>
       </c>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A352" s="5">
         <v>40603</v>
       </c>
@@ -7552,7 +7552,7 @@
         <v>0.2717</v>
       </c>
     </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A353" s="5">
         <v>40634</v>
       </c>
@@ -7572,7 +7572,7 @@
         <v>0.16539999999999999</v>
       </c>
     </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A354" s="5">
         <v>40664</v>
       </c>
@@ -7592,7 +7592,7 @@
         <v>0.2455</v>
       </c>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A355" s="5">
         <v>40695</v>
       </c>
@@ -7612,7 +7612,7 @@
         <v>9.3899999999999997E-2</v>
       </c>
     </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A356" s="5">
         <v>40725</v>
       </c>
@@ -7632,7 +7632,7 @@
         <v>0.1077</v>
       </c>
     </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A357" s="5">
         <v>40756</v>
       </c>
@@ -7652,7 +7652,7 @@
         <v>0.1767</v>
       </c>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A358" s="5">
         <v>40787</v>
       </c>
@@ -7672,7 +7672,7 @@
         <v>7.1999999999999995E-2</v>
       </c>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A359" s="5">
         <v>40817</v>
       </c>
@@ -7692,7 +7692,7 @@
         <v>9.8900000000000002E-2</v>
       </c>
     </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A360" s="5">
         <v>40848</v>
       </c>
@@ -7712,7 +7712,7 @@
         <v>0.1172</v>
       </c>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A361" s="5">
         <v>40878</v>
       </c>
@@ -7732,7 +7732,7 @@
         <v>1.24E-2</v>
       </c>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A362" s="5">
         <v>40909</v>
       </c>
@@ -7752,7 +7752,7 @@
         <v>5.5999999999999999E-3</v>
       </c>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A363" s="5">
         <v>40940</v>
       </c>
@@ -7772,7 +7772,7 @@
         <v>-0.16689999999999999</v>
       </c>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A364" s="5">
         <v>40969</v>
       </c>
@@ -7792,7 +7792,7 @@
         <v>0.104</v>
       </c>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A365" s="5">
         <v>41000</v>
       </c>
@@ -7812,7 +7812,7 @@
         <v>-3.15E-2</v>
       </c>
     </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A366" s="5">
         <v>41030</v>
       </c>
@@ -7832,7 +7832,7 @@
         <v>-6.5199999999999994E-2</v>
       </c>
     </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A367" s="5">
         <v>41061</v>
       </c>
@@ -7852,7 +7852,7 @@
         <v>-6.2300000000000001E-2</v>
       </c>
     </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A368" s="5">
         <v>41091</v>
       </c>
@@ -7872,7 +7872,7 @@
         <v>-3.1399999999999997E-2</v>
       </c>
     </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A369" s="5">
         <v>41122</v>
       </c>
@@ -7892,7 +7892,7 @@
         <v>-0.1147</v>
       </c>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A370" s="5">
         <v>41153</v>
       </c>
@@ -7912,7 +7912,7 @@
         <v>-4.02E-2</v>
       </c>
     </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A371" s="5">
         <v>41183</v>
       </c>
@@ -7932,7 +7932,7 @@
         <v>0.10340000000000001</v>
       </c>
     </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A372" s="5">
         <v>41214</v>
       </c>
@@ -7952,7 +7952,7 @@
         <v>-1.89E-2</v>
       </c>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A373" s="5">
         <v>41244</v>
       </c>
@@ -7972,7 +7972,7 @@
         <v>8.2000000000000007E-3</v>
       </c>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A374" s="5">
         <v>41275</v>
       </c>
@@ -7992,7 +7992,7 @@
         <v>8.8900000000000007E-2</v>
       </c>
     </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A375" s="5">
         <v>41306</v>
       </c>
@@ -8012,7 +8012,7 @@
         <v>0.21640000000000001</v>
       </c>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A376" s="5">
         <v>41334</v>
       </c>
@@ -8032,7 +8032,7 @@
         <v>-0.158</v>
       </c>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A377" s="5">
         <v>41365</v>
       </c>
@@ -8052,7 +8052,7 @@
         <v>3.2199999999999999E-2</v>
       </c>
     </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A378" s="5">
         <v>41395</v>
       </c>
@@ -8072,7 +8072,7 @@
         <v>-1.9E-2</v>
       </c>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A379" s="5">
         <v>41426</v>
       </c>
@@ -8092,7 +8092,7 @@
         <v>6.7999999999999996E-3</v>
       </c>
     </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A380" s="5">
         <v>41456</v>
       </c>
@@ -8112,7 +8112,7 @@
         <v>8.6800000000000002E-2</v>
       </c>
     </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A381" s="5">
         <v>41487</v>
       </c>
@@ -8132,7 +8132,7 @@
         <v>1.6199999999999999E-2</v>
       </c>
     </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A382" s="5">
         <v>41518</v>
       </c>
@@ -8152,7 +8152,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A383" s="5">
         <v>41548</v>
       </c>
@@ -8172,7 +8172,7 @@
         <v>-7.0499999999999993E-2</v>
       </c>
     </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A384" s="5">
         <v>41579</v>
       </c>
@@ -8192,7 +8192,7 @@
         <v>7.4000000000000003E-3</v>
       </c>
     </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A385" s="5">
         <v>41609</v>
       </c>
@@ -8212,7 +8212,7 @@
         <v>3.4299999999999997E-2</v>
       </c>
     </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A386" s="5">
         <v>41640</v>
       </c>
@@ -8232,7 +8232,7 @@
         <v>1.18E-2</v>
       </c>
     </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A387" s="5">
         <v>41671</v>
       </c>
@@ -8252,7 +8252,7 @@
         <v>-5.3800000000000001E-2</v>
       </c>
     </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A388" s="5">
         <v>41699</v>
       </c>
@@ -8275,7 +8275,7 @@
         <v>7.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A389" s="5">
         <v>41730</v>
       </c>
@@ -8298,7 +8298,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A390" s="5">
         <v>41760</v>
       </c>
@@ -8321,7 +8321,7 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A391" s="5">
         <v>41791</v>
       </c>
@@ -8344,7 +8344,7 @@
         <v>1.4E-2</v>
       </c>
     </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A392" s="5">
         <v>41821</v>
       </c>
@@ -8367,7 +8367,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A393" s="5">
         <v>41852</v>
       </c>
@@ -8390,7 +8390,7 @@
         <v>5.8000000000000003E-2</v>
       </c>
     </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A394" s="5">
         <v>41883</v>
       </c>
@@ -8413,7 +8413,7 @@
         <v>9.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A395" s="5">
         <v>41913</v>
       </c>
@@ -8436,7 +8436,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A396" s="5">
         <v>41944</v>
       </c>
@@ -8459,7 +8459,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A397" s="5">
         <v>41974</v>
       </c>
@@ -8482,7 +8482,7 @@
         <v>3.6999999999999998E-2</v>
       </c>
     </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A398" s="5">
         <v>42005</v>
       </c>
@@ -8505,7 +8505,7 @@
         <v>-2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A399" s="5">
         <v>42036</v>
       </c>
@@ -8528,7 +8528,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A400" s="5">
         <v>42064</v>
       </c>
@@ -8551,7 +8551,7 @@
         <v>-6.7000000000000004E-2</v>
       </c>
     </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A401" s="5">
         <v>42095</v>
       </c>
@@ -8574,7 +8574,7 @@
         <v>-8.8999999999999996E-2</v>
       </c>
     </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A402" s="5">
         <v>42125</v>
       </c>
@@ -8597,7 +8597,7 @@
         <v>-0.11700000000000001</v>
       </c>
     </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A403" s="5">
         <v>42156</v>
       </c>
@@ -8620,7 +8620,7 @@
         <v>-3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A404" s="5">
         <v>42186</v>
       </c>
@@ -8643,7 +8643,7 @@
         <v>-0.13900000000000001</v>
       </c>
     </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A405" s="5">
         <v>42217</v>
       </c>
@@ -8666,7 +8666,7 @@
         <v>-0.11899999999999999</v>
       </c>
     </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A406" s="5">
         <v>42248</v>
       </c>
@@ -8689,7 +8689,7 @@
         <v>-0.14799999999999999</v>
       </c>
     </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A407" s="5">
         <v>42278</v>
       </c>
@@ -8712,7 +8712,7 @@
         <v>-0.14599999999999999</v>
       </c>
     </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A408" s="5">
         <v>42309</v>
       </c>
@@ -8735,7 +8735,7 @@
         <v>-0.11</v>
       </c>
     </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A409" s="5">
         <v>42339</v>
       </c>
@@ -8758,7 +8758,7 @@
         <v>-0.16900000000000001</v>
       </c>
     </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A410" s="5">
         <v>42370</v>
       </c>
@@ -8781,7 +8781,7 @@
         <v>-0.13900000000000001</v>
       </c>
     </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A411" s="5">
         <v>42401</v>
       </c>
@@ -8804,7 +8804,7 @@
         <v>-0.13</v>
       </c>
     </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A412" s="5">
         <v>42430</v>
       </c>
@@ -8827,7 +8827,7 @@
         <v>-0.11799999999999999</v>
       </c>
     </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A413" s="5">
         <v>42461</v>
       </c>
@@ -8850,7 +8850,7 @@
         <v>-0.114</v>
       </c>
     </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A414" s="5">
         <v>42491</v>
       </c>
@@ -8873,7 +8873,7 @@
         <v>-6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A415" s="5">
         <v>42522</v>
       </c>
@@ -8896,7 +8896,7 @@
         <v>-9.6000000000000002E-2</v>
       </c>
     </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A416" s="5">
         <v>42552</v>
       </c>
@@ -8919,7 +8919,7 @@
         <v>-2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A417" s="5">
         <v>42583</v>
       </c>
@@ -8942,7 +8942,7 @@
         <v>1.2E-2</v>
       </c>
     </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A418" s="5">
         <v>42614</v>
       </c>
@@ -8965,7 +8965,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A419" s="5">
         <v>42644</v>
       </c>
@@ -8988,7 +8988,7 @@
         <v>-1.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A420" s="5">
         <v>42675</v>
       </c>
@@ -9011,7 +9011,7 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A421" s="5">
         <v>42705</v>
       </c>
@@ -9034,7 +9034,7 @@
         <v>0.121</v>
       </c>
     </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A422" s="5">
         <v>42736</v>
       </c>
@@ -9057,7 +9057,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A423" s="5">
         <v>42767</v>
       </c>
@@ -9080,7 +9080,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A424" s="5">
         <v>42795</v>
       </c>
@@ -9103,7 +9103,7 @@
         <v>0.27700000000000002</v>
       </c>
     </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A425" s="5">
         <v>42826</v>
       </c>
@@ -9126,7 +9126,7 @@
         <v>0.13200000000000001</v>
       </c>
     </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A426" s="5">
         <v>42856</v>
       </c>
@@ -9149,7 +9149,7 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A427" s="5">
         <v>42887</v>
       </c>
@@ -9172,7 +9172,7 @@
         <v>8.4000000000000005E-2</v>
       </c>
     </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A428" s="5">
         <v>42917</v>
       </c>
@@ -9195,7 +9195,7 @@
         <v>0.13</v>
       </c>
     </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A429" s="5">
         <v>42948</v>
       </c>
@@ -9218,7 +9218,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A430" s="5">
         <v>42979</v>
       </c>
@@ -9241,7 +9241,7 @@
         <v>0.127</v>
       </c>
     </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A431" s="5">
         <v>43009</v>
       </c>
@@ -9264,7 +9264,7 @@
         <v>0.28100000000000003</v>
       </c>
     </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A432" s="5">
         <v>43040</v>
       </c>
@@ -9287,7 +9287,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A433" s="5">
         <v>43070</v>
       </c>
@@ -9310,7 +9310,7 @@
         <v>0.14000000000000001</v>
       </c>
     </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A434" s="5">
         <v>43101</v>
       </c>
@@ -9333,7 +9333,7 @@
         <v>0.14799999999999999</v>
       </c>
     </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A435" s="5">
         <v>43132</v>
       </c>
@@ -9356,7 +9356,7 @@
         <v>0.153</v>
       </c>
     </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A436" s="5">
         <v>43160</v>
       </c>
@@ -9379,7 +9379,7 @@
         <v>-1.2E-2</v>
       </c>
     </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A437" s="5">
         <v>43191</v>
       </c>
@@ -9402,7 +9402,7 @@
         <v>0.16700000000000001</v>
       </c>
     </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A438" s="5">
         <v>43221</v>
       </c>
@@ -9425,7 +9425,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A439" s="5">
         <v>43252</v>
       </c>
@@ -9448,7 +9448,7 @@
         <v>0.14199999999999999</v>
       </c>
     </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A440" s="5">
         <v>43282</v>
       </c>
@@ -9471,7 +9471,7 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A441" s="5">
         <v>43313</v>
       </c>
@@ -9494,7 +9494,7 @@
         <v>4.7E-2</v>
       </c>
     </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A442" s="5">
         <v>43344</v>
       </c>
@@ -9517,7 +9517,7 @@
         <v>1.9E-2</v>
       </c>
     </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A443" s="5">
         <v>43374</v>
       </c>
@@ -9540,7 +9540,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A444" s="5">
         <v>43405</v>
       </c>
@@ -9563,7 +9563,7 @@
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A445" s="5">
         <v>43435</v>
       </c>
@@ -9586,7 +9586,7 @@
         <v>-3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A446" s="5">
         <v>43466</v>
       </c>
@@ -9609,7 +9609,7 @@
         <v>-0.03</v>
       </c>
     </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A447" s="5">
         <v>43497</v>
       </c>
@@ -9632,7 +9632,7 @@
         <v>-3.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A448" s="5">
         <v>43525</v>
       </c>
@@ -9655,7 +9655,7 @@
         <v>-8.7999999999999995E-2</v>
       </c>
     </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A449" s="5">
         <v>43556</v>
       </c>
@@ -9678,7 +9678,7 @@
         <v>-4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A450" s="5">
         <v>43586</v>
       </c>
@@ -9701,7 +9701,7 @@
         <v>-3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A451" s="5">
         <v>43617</v>
       </c>
@@ -9724,7 +9724,7 @@
         <v>-4.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A452" s="5">
         <v>43647</v>
       </c>
@@ -9747,7 +9747,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A453" s="5">
         <v>43678</v>
       </c>
@@ -9770,7 +9770,7 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A454" s="5">
         <v>43709</v>
       </c>
@@ -9793,7 +9793,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A455" s="5">
         <v>43739</v>
       </c>
@@ -9816,7 +9816,7 @@
         <v>-4.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A456" s="5">
         <v>43770</v>
       </c>
@@ -9839,7 +9839,7 @@
         <v>-1.4999999999999999E-2</v>
       </c>
     </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A457" s="5">
         <v>43800</v>
       </c>
@@ -9862,7 +9862,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
     </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A458" s="5">
         <v>43831</v>
       </c>
@@ -9885,7 +9885,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A459" s="5">
         <v>43862</v>
       </c>
@@ -9908,7 +9908,7 @@
         <v>-7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A460" s="5">
         <v>43891</v>
       </c>
@@ -9931,7 +9931,7 @@
         <v>0.249</v>
       </c>
     </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A461" s="5">
         <v>43922</v>
       </c>
@@ -9954,7 +9954,7 @@
         <v>-6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A462" s="5">
         <v>43952</v>
       </c>
@@ -9977,7 +9977,7 @@
         <v>-1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A463" s="5">
         <v>43983</v>
       </c>
@@ -10000,7 +10000,7 @@
         <v>-0.02</v>
       </c>
     </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A464" s="5">
         <v>44013</v>
       </c>
@@ -10023,7 +10023,7 @@
         <v>-3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A465" s="5">
         <v>44044</v>
       </c>
@@ -10046,7 +10046,7 @@
         <v>4.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A466" s="5">
         <v>44075</v>
       </c>
@@ -10069,7 +10069,7 @@
         <v>8.3000000000000004E-2</v>
       </c>
     </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A467" s="5">
         <v>44105</v>
       </c>
@@ -10092,7 +10092,7 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A468" s="5">
         <v>44136</v>
       </c>
@@ -10115,7 +10115,7 @@
         <v>0.112</v>
       </c>
     </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A469" s="5">
         <v>44166</v>
       </c>
@@ -10138,7 +10138,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A470" s="5">
         <v>44197</v>
       </c>
@@ -10161,7 +10161,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A471" s="5">
         <v>44228</v>
       </c>
@@ -10184,7 +10184,7 @@
         <v>0.36799999999999999</v>
       </c>
     </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A472" s="5">
         <v>44256</v>
       </c>
@@ -10207,7 +10207,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A473" s="5">
         <v>44287</v>
       </c>
@@ -10230,7 +10230,7 @@
         <v>0.27100000000000002</v>
       </c>
     </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A474" s="5">
         <v>44317</v>
       </c>
@@ -10253,7 +10253,7 @@
         <v>0.38700000000000001</v>
       </c>
     </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A475" s="5">
         <v>44348</v>
       </c>
@@ -10276,7 +10276,7 @@
         <v>0.38600000000000001</v>
       </c>
     </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A476" s="5">
         <v>44378</v>
       </c>
@@ -10299,7 +10299,7 @@
         <v>0.35099999999999998</v>
       </c>
     </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A477" s="5">
         <v>44409</v>
       </c>
@@ -10322,7 +10322,7 @@
         <v>0.34699999999999998</v>
       </c>
     </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A478" s="5">
         <v>44440</v>
       </c>
@@ -10345,7 +10345,7 @@
         <v>0.26900000000000002</v>
       </c>
     </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A479" s="5">
         <v>44470</v>
       </c>
@@ -10368,7 +10368,7 @@
         <v>0.29199999999999998</v>
       </c>
     </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A480" s="5">
         <v>44501</v>
       </c>
@@ -10391,7 +10391,7 @@
         <v>0.246</v>
       </c>
     </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A481" s="5">
         <v>44531</v>
       </c>
@@ -10414,7 +10414,7 @@
         <v>0.30199999999999999</v>
       </c>
     </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A482" s="5">
         <v>44562</v>
       </c>
@@ -10437,7 +10437,7 @@
         <v>0.23400000000000001</v>
       </c>
     </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A483" s="5">
         <v>44593</v>
       </c>
@@ -10460,7 +10460,7 @@
         <v>0.16700000000000001</v>
       </c>
     </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A484" s="5">
         <v>44621</v>
       </c>
@@ -10483,7 +10483,7 @@
         <v>0.34799999999999998</v>
       </c>
     </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A485" s="5">
         <v>44652</v>
       </c>
@@ -10506,7 +10506,7 @@
         <v>0.21299999999999999</v>
       </c>
     </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A486" s="5">
         <v>44682</v>
       </c>
@@ -10529,7 +10529,7 @@
         <v>0.188</v>
       </c>
     </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A487" s="5">
         <v>44713</v>
       </c>
@@ -10552,7 +10552,7 @@
         <v>0.125</v>
       </c>
     </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A488" s="5">
         <v>44743</v>
       </c>
@@ -10575,7 +10575,7 @@
         <v>0.152</v>
       </c>
     </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A489" s="5">
         <v>44774</v>
       </c>
@@ -10598,7 +10598,7 @@
         <v>0.14199999999999999</v>
       </c>
     </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A490" s="5">
         <v>44805</v>
       </c>
@@ -10621,7 +10621,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A491" s="5">
         <v>44835</v>
       </c>
@@ -10644,7 +10644,7 @@
         <v>-5.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A492" s="5">
         <v>44866</v>
       </c>
@@ -10667,7 +10667,7 @@
         <v>-5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A493" s="5">
         <v>44896</v>
       </c>
@@ -10690,7 +10690,7 @@
         <v>-0.13100000000000001</v>
       </c>
     </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A494" s="5">
         <v>44927</v>
       </c>
@@ -10713,7 +10713,7 @@
         <v>-0.121</v>
       </c>
     </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A495" s="5">
         <v>44958</v>
       </c>
@@ -10736,7 +10736,7 @@
         <v>-0.21199999999999999</v>
       </c>
     </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A496" s="5">
         <v>44986</v>
       </c>
@@ -10759,7 +10759,7 @@
         <v>-0.17100000000000001</v>
       </c>
     </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A497" s="5">
         <v>45017</v>
       </c>
@@ -10782,7 +10782,7 @@
         <v>-0.191</v>
       </c>
     </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A498" s="5">
         <v>45047</v>
       </c>
@@ -10805,7 +10805,7 @@
         <v>-0.13300000000000001</v>
       </c>
     </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A499" s="5">
         <v>45078</v>
       </c>
@@ -10828,7 +10828,7 @@
         <v>-0.14099999999999999</v>
       </c>
     </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A500" s="5">
         <v>45108</v>
       </c>
@@ -10851,7 +10851,7 @@
         <v>-0.23400000000000001</v>
       </c>
     </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A501" s="5">
         <v>45139</v>
       </c>
@@ -10874,7 +10874,7 @@
         <v>-0.104</v>
       </c>
     </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A502" s="5">
         <v>45170</v>
       </c>
@@ -10897,7 +10897,7 @@
         <v>-7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A503" s="5">
         <v>45200</v>
       </c>
@@ -10920,7 +10920,7 @@
         <v>3.4000000000000002E-2</v>
       </c>
     </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A504" s="5">
         <v>45231</v>
       </c>
@@ -10943,7 +10943,7 @@
         <v>-4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A505" s="5">
         <v>45261</v>
       </c>
@@ -10966,7 +10966,7 @@
         <v>3.7999999999999999E-2</v>
       </c>
     </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A506" s="5">
         <v>45292</v>
       </c>
@@ -10989,7 +10989,7 @@
         <v>0.11799999999999999</v>
       </c>
     </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A507" s="5">
         <v>45323</v>
       </c>
@@ -11012,7 +11012,7 @@
         <v>0.18099999999999999</v>
       </c>
     </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A508" s="5">
         <v>45352</v>
       </c>
@@ -11035,7 +11035,7 @@
         <v>1.2999999999999999E-2</v>
       </c>
     </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A509" s="5">
         <v>45383</v>
       </c>
@@ -11058,7 +11058,7 @@
         <v>0.189</v>
       </c>
     </row>
-    <row r="510" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A510" s="5">
         <v>45413</v>
       </c>
@@ -11081,7 +11081,7 @@
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A511" s="5">
         <v>45444</v>
       </c>
@@ -11104,7 +11104,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A512" s="5">
         <v>45474</v>
       </c>
@@ -11127,7 +11127,7 @@
         <v>0.23499999999999999</v>
       </c>
     </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A513" s="5">
         <v>45505</v>
       </c>
@@ -11150,7 +11150,7 @@
         <v>3.1E-2</v>
       </c>
     </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A514" s="5">
         <v>45536</v>
       </c>
@@ -11173,7 +11173,7 @@
         <v>0.16800000000000001</v>
       </c>
     </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A515" s="5">
         <v>45566</v>
       </c>
@@ -11196,7 +11196,7 @@
         <v>4.4999999999999998E-2</v>
       </c>
     </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A516" s="5">
         <v>45597</v>
       </c>
@@ -11219,7 +11219,7 @@
         <v>8.4000000000000005E-2</v>
       </c>
     </row>
-    <row r="517" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A517" s="5">
         <v>45627</v>
       </c>
@@ -11242,7 +11242,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="518" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A518" s="5">
         <v>45658</v>
       </c>
@@ -11265,7 +11265,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="519" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A519" s="5">
         <v>45689</v>
       </c>
@@ -11288,7 +11288,7 @@
         <v>4.3999999999999997E-2</v>
       </c>
     </row>
-    <row r="520" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A520" s="5">
         <v>45717</v>
       </c>
@@ -11311,7 +11311,7 @@
         <v>0.315</v>
       </c>
     </row>
-    <row r="521" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A521" s="5">
         <v>45748</v>
       </c>
@@ -11334,7 +11334,7 @@
         <v>0.186</v>
       </c>
     </row>
-    <row r="522" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A522" s="5">
         <v>45778</v>
       </c>
@@ -11354,7 +11354,7 @@
         <v>0.29899999999999999</v>
       </c>
     </row>
-    <row r="523" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A523" s="5">
         <v>45809</v>
       </c>
@@ -11374,7 +11374,7 @@
         <v>0.38600000000000001</v>
       </c>
     </row>
-    <row r="524" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A524" s="5">
         <v>45839</v>
       </c>
@@ -11397,7 +11397,7 @@
         <v>0.33700000000000002</v>
       </c>
     </row>
-    <row r="525" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A525" s="5">
         <v>45870</v>
       </c>
@@ -11420,7 +11420,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="526" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A526" s="5">
         <v>45901</v>
       </c>
@@ -11443,7 +11443,7 @@
         <v>0.34100000000000003</v>
       </c>
     </row>
-    <row r="527" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A527" s="5">
         <v>45931</v>
       </c>
@@ -11466,7 +11466,7 @@
         <v>0.33800000000000002</v>
       </c>
     </row>
-    <row r="528" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A528" s="5">
         <v>45962</v>
       </c>
@@ -11489,7 +11489,7 @@
         <v>0.497</v>
       </c>
     </row>
-    <row r="529" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A529" s="5">
         <v>45992</v>
       </c>
@@ -11512,7 +11512,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="530" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A530" s="5">
         <v>46023</v>
       </c>
@@ -11535,7 +11535,7 @@
         <v>0.434</v>
       </c>
     </row>
-    <row r="531" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A531" s="5">
         <v>46054</v>
       </c>
@@ -11548,12 +11548,41 @@
       <c r="D531" s="6" t="s">
         <v>6</v>
       </c>
+      <c r="E531" s="11">
+        <v>0.20599999999999999</v>
+      </c>
+      <c r="F531" s="11">
+        <v>0.28799999999999998</v>
+      </c>
       <c r="G531" s="11">
         <v>0.69899999999999995</v>
       </c>
     </row>
+    <row r="532" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A532" s="5">
+        <v>46082</v>
+      </c>
+      <c r="B532" s="5">
+        <v>46122</v>
+      </c>
+      <c r="C532" s="9">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D532" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E532" s="11">
+        <v>0.61799999999999999</v>
+      </c>
+      <c r="F532" s="11">
+        <v>0.33200000000000002</v>
+      </c>
+      <c r="G532" s="11">
+        <v>0.20599999999999999</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState ref="B2:G528">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:G528">
     <sortCondition ref="B2:B528"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -11565,12 +11594,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D57C3716-2D72-42CE-A393-1CB4772B0C37}">
   <dimension ref="B2:C3"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>8</v>
       </c>
@@ -11578,7 +11607,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
